--- a/data_extactor/batch_10_fa/trimmed/batch_0092_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0092_fa_trim.xlsx
@@ -513,12 +513,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>تولید و پردازش</t>
+          <t>تولید و فرآوری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>دید نزدیک | ثبات دست و بازو | چابکی دستی | هماهنگی چند اندام | دقت کنترل حرکتی | توجه انتخابی | حساسیت به مسئله</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | مهارت دستی | هماهنگی چند عضو | دقت کنترل | توجه انتخابی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان تجهیزات فرایندهای شیمیایی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های خردایش، سنگ‌زنی و پولیش | بچ‌سازان مواد غذایی | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌های صنعتی | تغذیه‌کنندگان و متصدیان تخلیه ماشین‌آلات صنعتی | اپراتورها و متصدیان دستگاه‌های بسته‌بندی و پرکن | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جداسازی، فیلتراسیون، شفاف‌سازی، ته‌نشینی و تقطیر</t>
+          <t>اپراتورها و متصدیان ماشین‌آلات و راکتورهای شیمیایی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تولیدکنندگان فرمولی و دسته‌ای مواد غذایی | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌های صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | ریاضیات</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | ریاضیات</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>تولید و پردازش</t>
+          <t>تولید و فرآوری</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>چابکی دستی | دید نزدیک | ثبات دست و بازو | مرتب‌سازی اطلاعات | قدرت ایستا | دقت کنترل حرکتی | انعطاف‌پذیری در طبقه‌بندی</t>
+          <t>مهارت دستی | بینایی نزدیک | ثبات دست و بازو | ترتیب‌دهی اطلاعات | قدرت ایستا | دقت کنترل | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>استفاده از ابزارهای دستی و کنترل فیزیکی تجهیزات | محیط سرپوشیده با تهویهٔ مطبوع | اهمیت بالای دقت در کار | ایستادن طولانی‌مدت | انجام حرکات تکراری | فشار زمانی</t>
+          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | صرف زمان برای ایستادن | صرف زمان برای انجام حرکات تکراری | فشار زمانی</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ور Bastه‌کنی | پرداخت‌کاران و صیقل‌کاران دستی | تغذیه‌کنندگان و متصدیان تخلیه ماشین‌آلات صنعتی | کارگران بسته‌بندی دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اره‌کشی چوب | چرخکاران و دوزندگان صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش منسوجات</t>
+          <t>تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران بسته‌بندی دستی | تنظیم‌کنندگان، متصدیان و اپراتورهای اره‌ چوب‌بری | چرخکاران صنعتی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -627,12 +627,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>تولید و پردازش | ریاضیات | مکانیک</t>
+          <t>تولید و فرآوری | ریاضیات | مکانیک</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>چابکی انگشتان | دقت کنترل حرکتی | دید نزدیک | ثبات دست و بازو | حساسیت به مسئله | چابکی دستی | هماهنگی چند اندام</t>
+          <t>مهارت انگشتان | دقت کنترل | بینایی نزدیک | ثبات دست و بازو | حساسیت به مسئله | مهارت دستی | هماهنگی چند عضو</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های خردایش، سنگ‌زنی و پولیش | برشکاران و پیرایشگران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تغذیه‌کنندگان و متصدیان تخلیه ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اره‌کشی چوب | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش منسوجات</t>
+          <t>تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | برشکاران و پیرایشگران دستی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | تنظیم‌کنندگان، متصدیان و اپراتورهای اره‌ چوب‌بری | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,22 +674,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>نرم‌افزار پایگاه داده عملیاتی | نرم‌افزار زمان‌بندی تولید | نرم‌افزار SAP | Microsoft Excel | Microsoft Office | Microsoft Outlook | Microsoft Word</t>
+          <t>نرم‌افزار پایگاه داده عملیاتی | نرم‌افزار Microsoft Office | نرم‌افزار SAP | Microsoft Excel | Microsoft Office | Microsoft Outlook</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>نظارت | سخن گفتن | تفکر انتقادی | شنیدن فعال | درک مطلب</t>
+          <t>نظارت | سخن گفتن | تفکر انتقادی | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>تولید و پردازش | مکانیک | رایانه و الکترونیک</t>
+          <t>تولید و فرآوری | مکانیک | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>سرعت ادراک | کنترل نرخ حرکت | زمان واکنش | ثبات دست و بازو | دید نزدیک | چابکی دستی | حساسیت به مسئله</t>
+          <t>سرعت ادراکی | کنترل نرخ | زمان عکس‌العمل | ثبات دست و بازو | بینایی نزدیک | مهارت دستی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های خردایش، سنگ‌زنی و پولیش | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن و کشش فلز و پلاستیک | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌های صنعتی | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و متصدیان تخلیه ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک</t>
+          <t>تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌های صنعتی | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | تفکر انتقادی | نظارت</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مکانیک | تولید و پردازش | ایمنی و امنیت عمومی</t>
+          <t>مکانیک | تولید و فرآوری | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | دقت کنترل حرکتی | درک کتبی | درک شفاهی | ثبات دست و بازو | دید نزدیک | توجه انتخابی</t>
+          <t>حساسیت به مسئله | دقت کنترل | درک کتبی | درک شفاهی | ثبات دست و بازو | بینایی نزدیک | توجه انتخابی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان تجهیزات فرایندهای شیمیایی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های خردایش، سنگ‌زنی و پولیش | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | اپراتورها و متصدیان دستگاه‌های برشته‌کاری، پخت و خشک‌کن مواد غذایی و تنباکو | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی فلز و پلاستیک | تغذیه‌کنندگان و متصدیان تخلیه ماشین‌آلات صنعتی | اپراتورها و متصدیان کوره‌های ذوب و تصفیه فلزات</t>
+          <t>اپراتورها و متصدیان ماشین‌آلات و راکتورهای شیمیایی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | اپراتورهای ماشین‌آلات برشته‌کاری، پخت و خشک‌کن مواد غذایی و توتون | تنظیم‌کاران و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | اپراتورها و متصدیان کوره‌های تصفیه و ذوب فلزات</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نگارش | سخن گفتن | درک مطلب | شنیدن فعال | نظارت</t>
+          <t>تفکر انتقادی | نگارش | سخن گفتن | درک مطلب | گوش دادن فعال | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>تولید و پردازش | زبان انگلیسی | خدمات مشتریان و خدمات فردی | مکانیک | ریاضیات</t>
+          <t>تولید و فرآوری | زبان انگلیسی | خدمات مشتری و شخصی | مکانیک | ریاضیات</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>دید نزدیک | سرعت ادراک | حساسیت به مسئله | انعطاف‌پذیری بستن الگو | مرتب‌سازی اطلاعات | درک کتبی | توجه انتخابی</t>
+          <t>بینایی نزدیک | سرعت ادراکی | حساسیت به مسئله | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | درک کتبی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>کارشناسان و تکنسین‌های کالیبراسیون | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران موتور و سایر ماشین‌آلات صنعتی | مکانیک‌های ماشین‌آلات صنعتی | تراشکاران و ماشین‌کاران صنعتی | کارشناسان و تکنسین‌های مهندسی مکانیک | توزین‌گران، متصدیان سنجش، بررسی‌کنندگان و نمونه‌برداران ثبتی</t>
+          <t>تکنسین‌ها و کارشناسان فنی کالیبراسیون | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک‌های ماشین‌آلات صنعتی | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | کارشناسان و تکنسین‌های مهندسی مکانیک | متصدیان توزین، سنجش، بازرسی و نمونه‌برداری ثبت اسناد</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | طراحی | تولید و پردازش | فروش و بازاریابی | مدیریت و امور اداری | هنرهای تجسمی</t>
+          <t>خدمات مشتری و شخصی | طراحی | تولید و فرآوری | فروش و بازاریابی | مدیریت و اداره | هنرهای زیبا</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دید نزدیک | چابکی انگشتان | ثبات دست و بازو | تجسم فضایی | ابتکار و اصالت | تشخیص تمایز رنگ‌ها | حساسیت به مسئله</t>
+          <t>بینایی نزدیک | مهارت انگشتان | ثبات دست و بازو | تجسم | اصالت | تشخیص رنگ بصری | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>هنرمندان صنایع دستی | قلم‌زنان و حکاکان | تراشکاران و صیقل‌دهندگان سنگ‌های قیمتی و الماس | پرداخت‌کاران و صیقل‌کاران دستی | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران (به‌جز فلز و پلاستیک) | برشکاران و سنگ‌تراشان سنگ‌های تزیینی و ساختمانی | قالب‌سازان و ابزارسازان صنعتی</t>
+          <t>هنرمندان صنایع دستی | حکاکان و اسیدکاران | تراشکاران و صیقل‌دهندگان سنگ‌های قیمتی و الماس | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | سنگ‌تراشان و حکاکان صنعتی سنگ | قالب‌سازان و ابزارسازان صنعتی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,22 +902,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>نرم‌افزار تخصصی طراحی گوهر GemCad | نرم‌افزار طراحی طلا و جواهر | نرم‌افزار پایگاه داده تشخیص و شناسایی سنگ‌های قیمتی | نرم‌افزار ردیابی موجودی | نرم‌افزار تجزیه و تحلیل اسپکتروفتومتر | نرم‌افزار مرورگر وب | نرم‌افزار حسابداری بازرگانی</t>
+          <t>نرم‌افزار تخصصی طراحی گوهر GemCad | نرم‌افزار طراحی طلا و جواهر | نرم‌افزار پایگاه داده تشخیص و شناسایی سنگ‌های قیمتی | نرم‌افزار ردیابی موجودی | نرم‌افزار تجزیه و تحلیل اسپکتروفتومتر | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نظارت | تفکر انتقادی</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | تولید و پردازش | زبان انگلیسی | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | تولید و فرآوری | زبان انگلیسی | ریاضیات</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>دید نزدیک | چابکی انگشتان | ثبات دست و بازو | تشخیص تمایز رنگ‌ها | حساسیت به مسئله | دقت کنترل حرکتی | چابکی دستی</t>
+          <t>بینایی نزدیک | مهارت انگشتان | ثبات دست و بازو | تشخیص رنگ بصری | حساسیت به مسئله | دقت کنترل | مهارت دستی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>برشکاران و پیرایشگران دستی | قلم‌زنان و حکاکان | پرداخت‌کاران و صیقل‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پرداخت و پولیش فلز و پلاستیک | جواهرسازان و سازندگان مصنوعات فلزی و سنگ‌های قیمتی | برشکاران و سنگ‌تراشان سنگ‌های تزیینی و ساختمانی | سنگ‌زن‌ها، سوهان‌کاران و تیزکنندگان ابزار</t>
+          <t>برشکاران و پیرایشگران دستی | حکاکان و اسیدکاران | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | جواهرسازان و سازندگان مصنوعات فلزی و سنگ‌های قیمتی | سنگ‌تراشان و حکاکان صنعتی سنگ | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | یادگیری فعال | سخن گفتن | شنیدن فعال</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | یادگیری فعال | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | طراحی | پزشکی و دندانپزشکی | تولید و پردازش | مکانیک | رایانه و الکترونیک</t>
+          <t>مدیریت و اداره | طراحی | پزشکی و دندان‌پزشکی | تولید و فرآوری | مکانیک | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>چابکی انگشتان | دید نزدیک | ثبات دست و بازو | دقت کنترل حرکتی | تجسم فضایی | استدلال قیاسی | چابکی دستی</t>
+          <t>مهارت انگشتان | بینایی نزدیک | ثبات دست و بازو | دقت کنترل | تجسم | استدلال قیاسی | مهارت دستی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>دستیاران دندانپزشک | دندانپزشکان عمومی | تکنسین‌های ساخت پروتز و اعضای مصنوعی پزشکی | تعمیرکاران تجهیزات پزشکی | تکنسین‌های آزمایشگاه و کارگاه ساخت عینک و اپتیک | متخصصان ارتز و پروتز | متخصصان پروتزهای دندانی</t>
+          <t>دستیاران دندان‌پزشک | دندان‌پزشکان عمومی | تکنسین‌های ساخت پروتز و اعضای مصنوعی پزشکی | تعمیرکاران تجهیزات پزشکی | تکنسین‌های آزمایشگاه و کارگاه ساخت عینک و قطعات اپتیک | ارتوپدهای فنی و سازندگان اعضای مصنوعی | متخصصان پروتزهای دندانی (پروستودنتیست‌ها)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | نظارت | یادگیری فعال | نگارش</t>
+          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>تولید و پردازش | خدمات مشتریان و خدمات فردی | زبان انگلیسی | مکانیک | طراحی | آموزش و تدریس | ریاضیات</t>
+          <t>تولید و فرآوری | خدمات مشتری و شخصی | زبان انگلیسی | مکانیک | طراحی | آموزش و پرورش | ریاضیات</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | دید نزدیک | تجسم فضایی | ثبات دست و بازو | چابکی انگشتان | چابکی دستی</t>
+          <t>درک شفاهی | حساسیت به مسئله | بینایی نزدیک | تجسم | ثبات دست و بازو | مهارت انگشتان | مهارت دستی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تکنسین‌های پروتزهای دندانی و لابراتوار دندانسازی | مونتاژکاران تجهیزات الکترومکانیکی | کارشناسان و تکنسین‌های مهندسی مکانیک | تعمیرکاران تجهیزات پزشکی | تکنسین‌های آزمایشگاه و کارگاه ساخت عینک و اپتیک | متخصصان ارتز و پروتز | سازندگان و تعمیرکاران کفش و مصنوعات چرمی</t>
+          <t>تکنسین‌های پروتزهای دندانی و لابراتوار دندانسازی | مونتاژکاران تجهیزات الکترومکانیکی | کارشناسان و تکنسین‌های مهندسی مکانیک | تعمیرکاران تجهیزات پزشکی | تکنسین‌های آزمایشگاه و کارگاه ساخت عینک و قطعات اپتیک | ارتوپدهای فنی و سازندگان اعضای مصنوعی | کارگران و تعمیرکاران کفش و چرم</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
